--- a/data/trans_bre/IP16A05-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Provincia-trans_bre.xlsx
@@ -602,7 +602,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-31,58; 12,08</t>
+          <t>-30,33; 12,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 38,54</t>
+          <t>-5,0; 42,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,77; -1,86</t>
+          <t>-32,68; -2,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,93; 44,35</t>
+          <t>0,44; 41,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-48,36; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -702,7 +702,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 18,33</t>
+          <t>-3,37; 18,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 11,74</t>
+          <t>-14,9; 11,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,32; -7,88</t>
+          <t>-45,03; -8,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 2,6</t>
+          <t>-7,68; 2,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 421,39</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-95,0; -28,14</t>
+          <t>-95,72; -26,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -802,7 +802,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,18; 11,76</t>
+          <t>-18,44; 11,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 36,15</t>
+          <t>-12,92; 34,45</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,19; 45,51</t>
+          <t>-9,31; 46,63</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 4,52</t>
+          <t>-11,41; 4,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-52,16; 409,48</t>
+          <t>-62,29; 322,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,12; 4,68</t>
+          <t>-29,36; 6,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,12; 12,46</t>
+          <t>-31,56; 12,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 24,76</t>
+          <t>-4,48; 26,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-49,5; 0,0</t>
+          <t>-50,13; 0,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-88,96; 308,64</t>
+          <t>-90,48; 350,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,71; —</t>
+          <t>-59,13; 827,45</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 46,71</t>
+          <t>-0,89; 47,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,7</t>
+          <t>0,0; 52,04</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,07</t>
+          <t>0,0; 40,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,77; 11,24</t>
+          <t>-29,16; 10,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-17,31; 26,37</t>
+          <t>-16,72; 28,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-34,95; 16,43</t>
+          <t>-40,24; 16,55</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 23,26</t>
+          <t>-12,25; 24,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 27,1</t>
+          <t>-1,98; 26,52</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-12,53; 16,5</t>
+          <t>-13,29; 16,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 29,58</t>
+          <t>-0,68; 29,54</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-59,96; —</t>
+          <t>-65,08; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-90,21; 592,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 764,07</t>
+          <t>-22,17; 710,87</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-15,55; 11,62</t>
+          <t>-14,83; 11,7</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 25,31</t>
+          <t>-15,43; 24,26</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 28,31</t>
+          <t>-4,66; 27,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-31,14; 0,0</t>
+          <t>-27,48; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-76,49; 151,09</t>
+          <t>-78,6; 170,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-60,6; 616,31</t>
+          <t>-70,68; 364,07</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-53,26; inf</t>
+          <t>-54,96; 1016,77</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 4,1</t>
+          <t>-7,1; 4,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 12,27</t>
+          <t>-1,72; 11,24</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,9; 5,05</t>
+          <t>-7,44; 6,3</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 8,97</t>
+          <t>-2,34; 9,35</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-54,63; 55,95</t>
+          <t>-55,29; 58,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 122,81</t>
+          <t>-12,74; 110,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-49,64; 57,54</t>
+          <t>-47,42; 70,09</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-34,49; 250,83</t>
+          <t>-35,55; 262,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A05-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Provincia-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-30,33; 12,76</t>
+          <t>-29,79; 14,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 42,12</t>
+          <t>-3,52; 40,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-32,68; -2,41</t>
+          <t>-32,91; -1,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,44; 41,25</t>
+          <t>0,5; 41,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-50,8; 1252,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 18,57</t>
+          <t>-6,18; 18,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-14,9; 11,88</t>
+          <t>-15,92; 12,03</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-45,03; -8,21</t>
+          <t>-44,02; -8,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 2,49</t>
+          <t>-7,37; 3,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 421,39</t>
+          <t>-100,0; 455,67</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-95,72; -26,52</t>
+          <t>-94,57; -23,17</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,44; 11,74</t>
+          <t>-18,02; 11,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 34,45</t>
+          <t>-10,59; 38,09</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-9,31; 46,63</t>
+          <t>-8,9; 46,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,41; 4,63</t>
+          <t>-12,21; 4,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-62,29; 322,42</t>
+          <t>-50,15; 507,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-29,36; 6,21</t>
+          <t>-31,5; 3,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-31,56; 12,92</t>
+          <t>-32,83; 12,34</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 26,26</t>
+          <t>-5,83; 24,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-50,13; 0,0</t>
+          <t>-53,87; 0,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-90,48; 350,16</t>
+          <t>-90,4; 233,05</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,13; 827,45</t>
+          <t>-59,36; 843,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 47,16</t>
+          <t>2,85; 48,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,04</t>
+          <t>0,0; 52,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,46</t>
+          <t>0,0; 38,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,16; 10,98</t>
+          <t>-29,54; 11,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,72; 28,61</t>
+          <t>-18,53; 24,51</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,24; 16,55</t>
+          <t>-40,03; 16,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,25; 24,41</t>
+          <t>-12,52; 22,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1260,12 +1260,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 26,52</t>
+          <t>-4,69; 26,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 16,01</t>
+          <t>-14,35; 15,12</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1275,12 +1275,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 29,54</t>
+          <t>1,1; 30,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-65,08; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-22,17; 710,87</t>
+          <t>-8,86; 733,39</t>
         </is>
       </c>
     </row>
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 11,7</t>
+          <t>-14,98; 10,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 24,26</t>
+          <t>-12,5; 25,33</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 27,44</t>
+          <t>-4,99; 27,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,48; 0,0</t>
+          <t>-31,72; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-78,6; 170,32</t>
+          <t>-74,4; 143,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,68; 364,07</t>
+          <t>-61,51; 489,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-54,96; 1016,77</t>
+          <t>-50,34; 1008,47</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,1; 4,3</t>
+          <t>-7,11; 4,15</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 11,24</t>
+          <t>-1,7; 11,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 6,3</t>
+          <t>-7,98; 5,69</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 9,35</t>
+          <t>-2,05; 9,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-55,29; 58,6</t>
+          <t>-54,61; 58,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-12,74; 110,81</t>
+          <t>-11,11; 118,22</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-47,42; 70,09</t>
+          <t>-47,57; 62,0</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-35,55; 262,05</t>
+          <t>-31,22; 280,6</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A05-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/IP16A05-Provincia-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos antibióticos</t>
+          <t>Menores que consumieron medicamentos antibióticos</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14,01</t>
+          <t>7,82</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>735,16%</t>
+          <t>443,89%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-29,79; 14,11</t>
+          <t>-31,58; 12,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 40,5</t>
+          <t>-5,12; 38,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-32,91; -1,02</t>
+          <t>-30,77; -1,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 41,88</t>
+          <t>0,71; 21,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-50,8; 1252,14</t>
+          <t>-48,36; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-1,94</t>
+          <t>-1,09</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-60,03%</t>
+          <t>-38,05%</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,18; 18,33</t>
+          <t>-5,9; 18,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,92; 12,03</t>
+          <t>-15,5; 11,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-44,02; -8,65</t>
+          <t>-44,32; -7,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 3,32</t>
+          <t>-5,03; 4,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -785,12 +785,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 455,67</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-94,57; -23,17</t>
+          <t>-95,0; -28,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>-1,38</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-27,77%</t>
+          <t>-40,11%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-18,02; 11,74</t>
+          <t>-18,18; 11,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 38,09</t>
+          <t>-11,62; 36,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 46,0</t>
+          <t>-9,19; 45,51</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,21; 4,53</t>
+          <t>-13,79; 4,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-50,15; 507,51</t>
+          <t>-52,16; 409,48</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-10,87</t>
+          <t>-11,03</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-31,5; 3,21</t>
+          <t>-31,12; 4,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-32,83; 12,34</t>
+          <t>-31,12; 12,46</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 24,43</t>
+          <t>-5,34; 24,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-53,87; 0,0</t>
+          <t>-50,9; 0,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-90,4; 233,05</t>
+          <t>-88,96; 308,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,36; 843,14</t>
+          <t>-49,71; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,6</t>
+          <t>14,09</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1065,17 +1065,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,85; 48,9</t>
+          <t>-0,71; 46,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,13</t>
+          <t>0,0; 53,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,6</t>
+          <t>0,0; 41,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,28</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-29,54; 11,18</t>
+          <t>-29,77; 11,24</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-18,53; 24,51</t>
+          <t>-17,31; 26,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 16,13</t>
+          <t>-34,95; 16,43</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-12,52; 22,94</t>
+          <t>-12,29; 24,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14,43</t>
+          <t>13,23</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>144,33%</t>
+          <t>128,88%</t>
         </is>
       </c>
     </row>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 26,91</t>
+          <t>-1,14; 27,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 15,12</t>
+          <t>-12,53; 16,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,1; 30,38</t>
+          <t>-3,14; 28,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-59,96; —</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-90,21; 592,0</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 733,39</t>
+          <t>-30,27; 687,53</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-6,17</t>
+          <t>-4,95</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1360,37 +1360,37 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,98; 10,79</t>
+          <t>-15,55; 11,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-12,5; 25,33</t>
+          <t>-13,06; 25,31</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 27,98</t>
+          <t>-4,7; 28,31</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-31,72; 0,0</t>
+          <t>-26,37; 0,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-74,4; 143,82</t>
+          <t>-76,49; 151,09</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-61,51; 489,16</t>
+          <t>-60,6; 616,31</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-50,34; 1008,47</t>
+          <t>-53,26; inf</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3,07</t>
+          <t>2,91</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>53,8%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 4,15</t>
+          <t>-7,03; 4,1</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 11,68</t>
+          <t>-1,44; 12,27</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,98; 5,69</t>
+          <t>-7,9; 5,05</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 9,4</t>
+          <t>-2,1; 7,83</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-54,61; 58,83</t>
+          <t>-54,63; 55,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 118,22</t>
+          <t>-10,51; 122,81</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-47,57; 62,0</t>
+          <t>-49,64; 57,54</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-31,22; 280,6</t>
+          <t>-30,09; 227,5</t>
         </is>
       </c>
     </row>
